--- a/artfynd/A 46769-2025 artfynd.xlsx
+++ b/artfynd/A 46769-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128751095</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128751108</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128749471</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128750630</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128750509</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128749586</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46769-2025 artfynd.xlsx
+++ b/artfynd/A 46769-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128751095</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128751108</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128749471</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128750630</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128750509</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128749586</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>128749564</v>
       </c>
       <c r="B8" t="n">
-        <v>57681</v>
+        <v>57708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128750514</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46769-2025 artfynd.xlsx
+++ b/artfynd/A 46769-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128751095</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128751108</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128749471</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128750630</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128750509</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128749586</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46769-2025 artfynd.xlsx
+++ b/artfynd/A 46769-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128751095</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128751108</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128749471</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128750630</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128750509</v>
       </c>
       <c r="B6" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128749586</v>
       </c>
       <c r="B7" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46769-2025 artfynd.xlsx
+++ b/artfynd/A 46769-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128751095</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128751108</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128749471</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128750630</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128750509</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128749586</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>128749564</v>
       </c>
       <c r="B8" t="n">
-        <v>57708</v>
+        <v>57712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128750514</v>
       </c>
       <c r="B9" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46769-2025 artfynd.xlsx
+++ b/artfynd/A 46769-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128751095</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128751108</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128749471</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128750630</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128750509</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128749586</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>128749564</v>
       </c>
       <c r="B8" t="n">
-        <v>57712</v>
+        <v>57715</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128750514</v>
       </c>
       <c r="B9" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46769-2025 artfynd.xlsx
+++ b/artfynd/A 46769-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128751095</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128751108</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128749471</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128750630</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128750509</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128749586</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46769-2025 artfynd.xlsx
+++ b/artfynd/A 46769-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128751095</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128751108</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128749471</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128750630</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128750509</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128749586</v>
       </c>
       <c r="B7" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46769-2025 artfynd.xlsx
+++ b/artfynd/A 46769-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128751095</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128751108</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128749471</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128750630</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128750509</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128749586</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>128749564</v>
       </c>
       <c r="B8" t="n">
-        <v>57715</v>
+        <v>57717</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128750514</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46769-2025 artfynd.xlsx
+++ b/artfynd/A 46769-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128751095</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128751108</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128749471</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128750630</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128750509</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128749586</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46769-2025 artfynd.xlsx
+++ b/artfynd/A 46769-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128751095</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128751108</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128749471</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>128750630</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128750509</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128749586</v>
       </c>
       <c r="B7" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>128749564</v>
       </c>
       <c r="B8" t="n">
-        <v>57717</v>
+        <v>57719</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128750514</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46769-2025 artfynd.xlsx
+++ b/artfynd/A 46769-2025 artfynd.xlsx
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128751095</v>
+        <v>128749564</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>57945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>795494</v>
+        <v>795498</v>
       </c>
       <c r="R2" t="n">
-        <v>7256615</v>
+        <v>7256619</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,47 +781,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128751108</v>
+        <v>128750514</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795487</v>
+        <v>795506</v>
       </c>
       <c r="R3" t="n">
-        <v>7256613</v>
+        <v>7256650</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +890,7 @@
         <v>128749471</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128750630</v>
+        <v>128749586</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,7 +1028,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795463</v>
+        <v>795527</v>
       </c>
       <c r="R5" t="n">
-        <v>7256630</v>
+        <v>7256606</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,6 +1083,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,7 +1117,7 @@
         <v>128750509</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128749586</v>
+        <v>128750630</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1255,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1279,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>795527</v>
+        <v>795463</v>
       </c>
       <c r="R7" t="n">
-        <v>7256606</v>
+        <v>7256630</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,11 +1310,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,42 +1336,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128749564</v>
+        <v>128751095</v>
       </c>
       <c r="B8" t="n">
-        <v>57719</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100110</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1390,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>795498</v>
+        <v>795494</v>
       </c>
       <c r="R8" t="n">
-        <v>7256619</v>
+        <v>7256615</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,42 +1447,47 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128750514</v>
+        <v>128751108</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>795506</v>
+        <v>795487</v>
       </c>
       <c r="R9" t="n">
-        <v>7256650</v>
+        <v>7256613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 46769-2025 artfynd.xlsx
+++ b/artfynd/A 46769-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,62 +887,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128749471</v>
+        <v>134738224</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>58136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skog NV Degermyrberget, Skog NV Degermyrberget, Nb</t>
+          <t>N Degermyrberget, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>795489</v>
+        <v>795490</v>
       </c>
       <c r="R4" t="n">
-        <v>7256622</v>
+        <v>7256641</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,12 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128749586</v>
+        <v>128749471</v>
       </c>
       <c r="B5" t="n">
         <v>99118</v>
@@ -1028,12 +1026,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1047,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795527</v>
+        <v>795489</v>
       </c>
       <c r="R5" t="n">
-        <v>7256606</v>
+        <v>7256622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,11 +1081,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128750509</v>
+        <v>128749586</v>
       </c>
       <c r="B6" t="n">
         <v>99118</v>
@@ -1144,12 +1137,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1163,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>795506</v>
+        <v>795527</v>
       </c>
       <c r="R6" t="n">
-        <v>7256650</v>
+        <v>7256606</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,6 +1192,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,7 +1223,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128750630</v>
+        <v>128750509</v>
       </c>
       <c r="B7" t="n">
         <v>99118</v>
@@ -1255,12 +1253,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1274,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>795463</v>
+        <v>795506</v>
       </c>
       <c r="R7" t="n">
-        <v>7256630</v>
+        <v>7256650</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1334,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128751095</v>
+        <v>128750630</v>
       </c>
       <c r="B8" t="n">
         <v>99118</v>
@@ -1366,7 +1364,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1385,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>795494</v>
+        <v>795463</v>
       </c>
       <c r="R8" t="n">
-        <v>7256615</v>
+        <v>7256630</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1445,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128751108</v>
+        <v>128751095</v>
       </c>
       <c r="B9" t="n">
         <v>99118</v>
@@ -1477,7 +1475,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1496,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>795487</v>
+        <v>795494</v>
       </c>
       <c r="R9" t="n">
-        <v>7256613</v>
+        <v>7256615</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,6 +1553,117 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128751108</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skog NV Degermyrberget, Skog NV Degermyrberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>795487</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7256613</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46769-2025 artfynd.xlsx
+++ b/artfynd/A 46769-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128749564</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128750514</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134738224</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128749471</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128749586</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128750509</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128750630</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128751095</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1664,8 +1709,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128751108</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>